--- a/Тест2/207.xlsx
+++ b/Тест2/207.xlsx
@@ -234,16 +234,16 @@
     <t xml:space="preserve">Boshqa isitmali kasallikdan farqlash</t>
   </si>
   <si>
-    <t xml:space="preserve">Tashxisni butunlay rad etish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Davolashni to'xtatish</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Antibiotik tanlash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaksina tanlash</t>
+    <t xml:space="preserve">Tashxisni butunlay rad etish uchun asos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Davolashni to'xtatish uchun asos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antibiotik tanlash uchun asos bo'ladi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaksina tanlash uchun asos bo'ladi</t>
   </si>
   <si>
     <t xml:space="preserve">To'g'ri javob: Boshqa isitmali kasallikdan farqlash. Hujumlar orasidagi tanaffus kasallikni boshqa surunkali isitmali holatlardan ajratishda foydali. Manba: Mavzu materiali (207.docx); Riedel S. va boshq. Jawetz, Melnick &amp; Adelberg's Medical Microbiology, 28-nashr (2019).</t>
